--- a/data/Pop+65ans_fr.xlsx
+++ b/data/Pop+65ans_fr.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\celin\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\utilisateur\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB418412-FFA4-4F61-A5AB-0E8B0D5B6FCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08420924-6441-4A92-8B4C-30630BE2BC50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuille 1" sheetId="2" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="56">
   <si>
     <t>TIME</t>
   </si>
@@ -185,6 +185,9 @@
   </si>
   <si>
     <t>Allemagne</t>
+  </si>
+  <si>
+    <t>Suède</t>
   </si>
 </sst>
 </file>
@@ -241,7 +244,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -264,11 +267,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB0B0B0"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB0B0B0"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -297,6 +311,15 @@
     <xf numFmtId="164" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -315,9 +338,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office 2013 – 2022">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -355,7 +378,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -461,7 +484,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -603,7 +626,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -611,7 +634,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:AH29"/>
+  <dimension ref="A1:AI29"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="11.4" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="29.88671875" customWidth="1"/>
@@ -2282,7 +2305,7 @@
         <v>1859677</v>
       </c>
     </row>
-    <row r="17" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:35" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
         <v>49</v>
       </c>
@@ -2386,7 +2409,7 @@
         <v>7667043</v>
       </c>
     </row>
-    <row r="18" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:35" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
         <v>50</v>
       </c>
@@ -2490,7 +2513,7 @@
         <v>2615344</v>
       </c>
     </row>
-    <row r="19" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:35" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
         <v>51</v>
       </c>
@@ -2594,7 +2617,7 @@
         <v>471800</v>
       </c>
     </row>
-    <row r="20" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:35" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
         <v>52</v>
       </c>
@@ -2698,7 +2721,7 @@
         <v>1018725</v>
       </c>
     </row>
-    <row r="21" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:35" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
         <v>53</v>
       </c>
@@ -2802,29 +2825,101 @@
         <v>1328817</v>
       </c>
     </row>
-    <row r="23" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:35" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="M22" s="11">
+        <v>1541254</v>
+      </c>
+      <c r="N22" s="12">
+        <v>1554335</v>
+      </c>
+      <c r="O22" s="12">
+        <v>1565377</v>
+      </c>
+      <c r="P22" s="12">
+        <v>1581437</v>
+      </c>
+      <c r="Q22" s="12">
+        <v>1608413</v>
+      </c>
+      <c r="R22" s="12">
+        <v>1645081</v>
+      </c>
+      <c r="S22" s="12">
+        <v>1690777</v>
+      </c>
+      <c r="T22" s="11">
+        <v>1737246</v>
+      </c>
+      <c r="U22" s="11">
+        <v>1784668</v>
+      </c>
+      <c r="V22" s="11">
+        <v>1828283</v>
+      </c>
+      <c r="W22" s="11">
+        <v>1872207</v>
+      </c>
+      <c r="X22" s="11">
+        <v>1912884</v>
+      </c>
+      <c r="Y22" s="11">
+        <v>1947227</v>
+      </c>
+      <c r="Z22" s="11">
+        <v>1976857</v>
+      </c>
+      <c r="AA22" s="11">
+        <v>2006146</v>
+      </c>
+      <c r="AB22" s="11">
+        <v>2035711</v>
+      </c>
+      <c r="AC22" s="11">
+        <v>2065367</v>
+      </c>
+      <c r="AD22" s="11">
+        <v>2088086</v>
+      </c>
+      <c r="AE22" s="11">
+        <v>2118766</v>
+      </c>
+      <c r="AF22" s="11">
+        <v>2147137</v>
+      </c>
+      <c r="AG22" s="11">
+        <v>2174752</v>
+      </c>
+      <c r="AH22" s="11">
+        <v>2206488</v>
+      </c>
+      <c r="AI22" s="11"/>
+    </row>
+    <row r="23" spans="1:35" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A23" s="1"/>
     </row>
-    <row r="24" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:35" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A24" s="1"/>
       <c r="B24" s="2"/>
     </row>
-    <row r="25" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:35" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A25" s="1"/>
     </row>
-    <row r="26" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:35" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A26" s="1"/>
       <c r="B26" s="2"/>
     </row>
-    <row r="27" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:35" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A27" s="1"/>
       <c r="B27" s="2"/>
     </row>
-    <row r="28" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:35" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A28" s="1"/>
       <c r="B28" s="2"/>
     </row>
-    <row r="29" spans="1:34" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:35" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A29" s="1"/>
       <c r="B29" s="2"/>
     </row>
